--- a/rte-rice-analysis/RTE_Rice_Benchmark.xlsx
+++ b/rte-rice-analysis/RTE_Rice_Benchmark.xlsx
@@ -11,13 +11,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Формати" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Наша лінійка" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Канали" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Калькулятор" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Застереження" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4b. Формат x грамаж" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Калькулятор" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Застереження" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Бренди'!$A$4:$M$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Наша лінійка'!$A$4:$O$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Канали'!$A$4:$D$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,23 +84,6 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="FF1E9EA6"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="FF303A5D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="FF717890"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
       <color rgb="FF303A5D"/>
       <sz val="10"/>
     </font>
@@ -113,7 +96,36 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="FFC94F7C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF303A5D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF717890"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="FFC4820A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF717890"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1E9EA6"/>
       <sz val="9"/>
     </font>
     <font>
@@ -122,20 +134,8 @@
       <color rgb="FF5D4B96"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="FFC94F7C"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="FF717890"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -150,6 +150,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1F4FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8B85F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6E3BC"/>
       </patternFill>
     </fill>
     <fill>
@@ -175,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,40 +210,74 @@
     <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -245,19 +289,16 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4362,26 +4403,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Карта каналів — 54 ідентифіковані продавці</t>
+          <t>Канали продажу: точка продажу × покупець</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Розширено відносно першого зрізу. Туристичний канал перелічено поіменно частково (28 із ~40).</t>
+          <t>Дві різні осі. Кількість точок продажу не дорівнює релевантності каналу для нас.</t>
         </is>
       </c>
     </row>
@@ -4393,1229 +4436,470 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Продавець</t>
+          <t>Тип точки продажу</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Які бренди тут стоять</t>
+          <t>Точок</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>Покупець і привід споживання</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>Статус для нас</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Мережевий роздріб (офлайн+онлайн)</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Продавці</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Продуктовий роздріб</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Мережі національного покриття</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>Масовий покупець · щоденне харчування</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>ЦІЛЬОВИЙ КАНАЛ</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Сільпо</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>11 позицій, усі Ben's Original</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Ціль 2-ї хвилі</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Онлайн-супермаркети й маркетплейси</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>MAUDAU</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Ben's · Henan · Bibigo · Clearspring · Portion</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Ціль 1-ї хвилі</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Онлайн-супермаркети й маркетплейси</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Rozetka</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Ben's · Henan · Bibigo · Clearspring · Portion</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Ціль 1-ї хвилі</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Онлайн-супермаркети й маркетплейси</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Prom</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Ben's · Henan · Bibigo · Clearspring · Portion</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Ціль 1-ї хвилі</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Онлайн-супермаркети й маркетплейси</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>zakaz.ua (17 мереж)</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Ben's · Henan · Bibigo · Clearspring · Portion</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Ціль 1-ї хвилі</t>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Онлайн-маркетплейси</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Універсальні майданчики</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Масовий покупець · плановане замовлення</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>ЦІЛЬОВИЙ КАНАЛ</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>MAUDAU · Rozetka · Prom</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Спеціалізований фудрітейл</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Азійські та етнічні магазини</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Покупець азійської кухні · знає категорію</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>ЦІЛЬОВИЙ КАНАЛ · ВХІД</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>Смак Кореї · Тайякі Март · Pulsar · Апетітаріум · Gurmissimo · Edison Lee · OMG! Asia · СНЕКІС · DCM · Скарби Азії · AsiaStyle · ASIA FOODS · Wèi Māo · AsianFoods · Asia Goods Store · SushiPovar · KladezGroup · Sweet Svitt · Товари з Іспанії · Asia Foods Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Outdoor- і мілітарі-рітейл</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Туристичні та військові магазини</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Турист і військовий · автономне харчування</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>НЕ НАШ ПОКУПЕЦЬ</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>ALANTUR · Highlander · ForCamp · Гайдамака · Freeride · MK-Sport · Daruy · Tactico · Лєєр · Activity та ще ~30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Онлайн-супермаркети й маркетплейси</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>GoToShop (агрегатор 8 мереж)</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Ben's · Henan · Bibigo · Clearspring · Portion</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Ціль 1-ї хвилі</t>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Мережі без жодної позиції категорії</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Смак Кореї</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Тайякі Март</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>АТБ, Novus, METRO, Varus, Ашан, Fora, «Таврія В», МегаМаркет, ЕКО маркет, Ultramarket, Восторг, Космос, WineTime, Фуршет, Близенько, Точка, Рукавичка</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Pulsar</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Агрегатори (у підрахунок точок продажу не входять)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Апетітаріум</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Gurmissimo</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Edison Lee</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>OMG! Asia</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>СНЕКІС</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>DCM</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Скарби Азії</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Sweet Svitt</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Товари з Іспанії</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>AsiaStyle</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>ASIA FOODS</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Wèi Māo</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>AsianFoods</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Asia Goods Store (Львів)</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>SushiPovar</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>KladezGroup</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>Азійські / етнічні фудшопи</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Asia Foods Trade (опт)</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Ottogi · Henan · Bibigo · саморозігрів · Gallina Blanca</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>ЦІЛЬ ПЕРШОГО ВХОДУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>ALANTUR</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Highlander</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>ForCamp</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Гайдамака</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Freeride</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>MK-Sport</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Daruy</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Tactico</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Лєєр</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Desna</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>Шериф</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>OXO</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>Palmer</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D44" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>ВсеОпт</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>Суренж</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>Klever-Shop</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Terra Incognita</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>Висот-Нік</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>СУХПАЙ</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D50" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>UPcompany</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>SportStorm</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>Kalush-Craft</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D53" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>110вольт</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D54" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>Клуб Мандрівник</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D55" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>Kamanti</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>Харчі ТМ</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>Туристичні та військові</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>Їжа в Похід</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>+ ще ~12 дрібних · Haidilao · Adventure Menu · усі сублімати</t>
-        </is>
-      </c>
-      <c r="D58" s="13" t="inlineStr">
-        <is>
-          <t>Не наш привід споживання</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>Мережі без жодної позиції категорії</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>АТБ, Novus, METRO, Varus, Ашан, Fora, Таврія В, МегаМаркет, ЕКО маркет, Ultramarket, Восторг, Космос, WineTime, Фуршет, Близенько, Точка, Рукавичка</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>zakaz.ua — 17 мереж · GoToShop — 8 мереж</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Модель формату і ваги — крос-таб 84 позицій</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Скільки позицій категорії має цей формат у цій ваговій смузі. 2 позиції без маси виключено.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Формат</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>80–99 г</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>100–149 г</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>150–199 г</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>200–249 г</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>250–299 г</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>300–349 г</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>350+ г</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Пауч · реторт</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="32">
+        <f>SUM(B5:H5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Чаша · стакан</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="29" t="n"/>
+      <c r="I6" s="32">
+        <f>SUM(B6:H6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Дойпак · сублімат</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="29" t="n"/>
+      <c r="H7" s="29" t="n"/>
+      <c r="I7" s="32">
+        <f>SUM(B7:H7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Коробка з нагрівачем</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="32">
+        <f>SUM(B8:H8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="B9" s="33">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="33">
+        <f>SUM(C5:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="33">
+        <f>SUM(D5:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="33">
+        <f>SUM(E5:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="33">
+        <f>SUM(F5:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="33">
+        <f>SUM(G5:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="33">
+        <f>SUM(H5:H8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>Медіана грн/100 г у смузі</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="n">
+        <v>171</v>
+      </c>
+      <c r="C11" s="35" t="n">
+        <v>264</v>
+      </c>
+      <c r="D11" s="35" t="n">
+        <v>348</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="37" t="n">
+        <v>94</v>
+      </c>
+      <c r="G11" s="37" t="n">
+        <v>104</v>
+      </c>
+      <c r="H11" s="36" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Що показує крос-таб</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>1. Порційне вікно 200–299 г — 22 позиції (пауч 14, чаша 8). Це полиця «обід на одну людину».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>2. Пауч живе тільки в 220–250 г: 14 із 19 позицій. Поза вікном — лише український реторт 350 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>3. Найщільніша клітинка — дойпак 100–149 г (16 позицій), але це сухий сублімат: інший привід.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>4. Найдешевший грам — смуга 200–249 г: 50 грн за 100 г, мінімум по всіх вагах.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5647,112 +4931,112 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Курс, грн/$</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
+      <c r="B4" s="39" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Бонус мережі, %</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="40" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Цільова маржа, %</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="40" t="n">
         <v>0.35</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Націнка мережі (x)</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="39" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Частка ціни для собівартості</t>
         </is>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="41">
         <f>1-B5-B6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Коеф. FOB → СС, 20′ FCL</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="42" t="n">
         <v>1.70740755878359</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>Коеф. FOB → СС, 40′ FCL</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="42" t="n">
         <v>1.530558573152913</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>Полиця = СС_грн × націнка / частка_СС</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>Множник СС → полиця</t>
         </is>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="44">
         <f>B7/B8</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>Множник FOB → полиця, 20′ FCL</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="45">
         <f>B9*B4*B12</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>Множник FOB → полиця, 40′ FCL</t>
         </is>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="45">
         <f>B10*B4*B12</f>
         <v/>
       </c>
@@ -5790,7 +5074,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="n">
+      <c r="A18" s="46" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -5798,51 +5082,51 @@
           <t>Ben's Original медіана 41 грн/100 г при 240 г</t>
         </is>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="47">
         <f>A18/$B$12</f>
         <v/>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="48">
         <f>C18/$B$4</f>
         <v/>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="49">
         <f>A18/$B$13</f>
         <v/>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="49">
         <f>A18/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="n">
+      <c r="A19" s="50" t="n">
         <v>109</v>
       </c>
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="51" t="inlineStr">
         <is>
           <t>Медіана формату «пауч» — найдешевший вхід у мережу</t>
         </is>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="52">
         <f>A19/$B$12</f>
         <v/>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="53">
         <f>C19/$B$4</f>
         <v/>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="54">
         <f>A19/$B$13</f>
         <v/>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="54">
         <f>A19/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="n">
+      <c r="A20" s="46" t="n">
         <v>119</v>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -5850,51 +5134,51 @@
           <t>Агресивний сценарій для стакана 150 г</t>
         </is>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="47">
         <f>A20/$B$12</f>
         <v/>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="48">
         <f>C20/$B$4</f>
         <v/>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="49">
         <f>A20/$B$13</f>
         <v/>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="49">
         <f>A20/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="n">
+      <c r="A21" s="50" t="n">
         <v>129</v>
       </c>
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B21" s="51" t="inlineStr">
         <is>
           <t>РЕКОМЕНДОВАНО для стакана 150 г — нижче Henan-медіани</t>
         </is>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="52">
         <f>A21/$B$12</f>
         <v/>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="53">
         <f>C21/$B$4</f>
         <v/>
       </c>
-      <c r="E21" s="39">
+      <c r="E21" s="54">
         <f>A21/$B$13</f>
         <v/>
       </c>
-      <c r="F21" s="39">
+      <c r="F21" s="54">
         <f>A21/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="n">
+      <c r="A22" s="46" t="n">
         <v>139</v>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -5902,51 +5186,51 @@
           <t>Поточна полиця стакана 150 г без переговорів</t>
         </is>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="47">
         <f>A22/$B$12</f>
         <v/>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="48">
         <f>C22/$B$4</f>
         <v/>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="49">
         <f>A22/$B$13</f>
         <v/>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="49">
         <f>A22/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="n">
+      <c r="A23" s="50" t="n">
         <v>155</v>
       </c>
-      <c r="B23" s="36" t="inlineStr">
+      <c r="B23" s="51" t="inlineStr">
         <is>
           <t>Паритет із Bibigo 210 г (135–189 грн)</t>
         </is>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="52">
         <f>A23/$B$12</f>
         <v/>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="53">
         <f>C23/$B$4</f>
         <v/>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="54">
         <f>A23/$B$13</f>
         <v/>
       </c>
-      <c r="F23" s="39">
+      <c r="F23" s="54">
         <f>A23/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="n">
+      <c r="A24" s="46" t="n">
         <v>179</v>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -5954,45 +5238,45 @@
           <t>Верх вікна мережевої полиці</t>
         </is>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="47">
         <f>A24/$B$12</f>
         <v/>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="48">
         <f>C24/$B$4</f>
         <v/>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="49">
         <f>A24/$B$13</f>
         <v/>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="49">
         <f>A24/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="n">
+      <c r="A25" s="50" t="n">
         <v>199</v>
       </c>
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="51" t="inlineStr">
         <is>
           <t>Ottogi −22 % — стеля для лотка ONE'S 200 г</t>
         </is>
       </c>
-      <c r="C25" s="37">
+      <c r="C25" s="52">
         <f>A25/$B$12</f>
         <v/>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="53">
         <f>C25/$B$4</f>
         <v/>
       </c>
-      <c r="E25" s="39">
+      <c r="E25" s="54">
         <f>A25/$B$13</f>
         <v/>
       </c>
-      <c r="F25" s="39">
+      <c r="F25" s="54">
         <f>A25/$B$14</f>
         <v/>
       </c>
@@ -6016,7 +5300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6068,264 +5352,264 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>Ціни конкурентів на полиці</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>ФАКТ</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Картки продавців, 17 мереж zakaz.ua, «Сільпо», Prom, Rozetka, MAUDAU, 22–23.09.2026</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>Формати, ваги, кількість SKU</t>
         </is>
       </c>
-      <c r="B6" s="45" t="inlineStr">
+      <c r="B6" s="57" t="inlineStr">
         <is>
           <t>ФАКТ</t>
         </is>
       </c>
-      <c r="C6" s="46" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>Картки продавців. 2 позиції без маси виключено з грн/100 г</t>
         </is>
       </c>
-      <c r="D6" s="47" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>Незначний</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="55" t="inlineStr">
         <is>
           <t>Обсяг імпорту 182 т</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>ФАКТ</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Eurostat Comext CN 1904 90 10 + UN Comtrade</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>Ємність роздрібу 87–110 млн грн</t>
         </is>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>ОЦІНКА</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C8" s="58" t="inlineStr">
         <is>
           <t>Імпорт × 2,2–2,8. Заміряних продажів немає</t>
         </is>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>Похибка ±30 % у бізнес-кейсі</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>Собівартість BSCM і CM Premium</t>
         </is>
       </c>
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>ФАКТ</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Комерційні пропозиції, RTE_Rice_Suppliers.pptx</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="44" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>FOB ONE'S International</t>
         </is>
       </c>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>ОЦІНКА</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="58" t="inlineStr">
         <is>
           <t>Виведено з СС за коефіцієнтом 1,7074. Постачальник FOB не розкрив</t>
         </is>
       </c>
-      <c r="D10" s="47" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>Рекомендація по Fried Rice 200 г може бути хибною</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>Коеф. FOB → СС = 1,7074</t>
         </is>
       </c>
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>РОЗРАХУНОК</t>
         </is>
       </c>
-      <c r="C11" s="42" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>СС / FOB для BSCM Jasmine 240 г, перевірено на 15 SKU</t>
         </is>
       </c>
-      <c r="D11" s="43" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>Зсув усіх цільових FOB</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="44" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>Мито 10 % у собівартості</t>
         </is>
       </c>
-      <c r="B12" s="50" t="inlineStr">
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>ПРИПУЩЕННЯ</t>
         </is>
       </c>
-      <c r="C12" s="46" t="inlineStr">
+      <c r="C12" s="58" t="inlineStr">
         <is>
           <t>Зазначено в RTE_Rice_Suppliers. Первинне джерело не наведено</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>±27 грн на полиці</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t>Імпортний ПДВ 20 % у СС</t>
         </is>
       </c>
-      <c r="B13" s="51" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>РИЗИК</t>
         </is>
       </c>
-      <c r="C13" s="42" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Ймовірне задвоєння: ПДВ і у витратах, і в ціні «вже з ПДВ»</t>
         </is>
       </c>
-      <c r="D13" s="43" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>СС −16,7 %, полиця пауча 157 → 131 грн</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="44" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>Бонус мережі 25 %</t>
         </is>
       </c>
-      <c r="B14" s="50" t="inlineStr">
+      <c r="B14" s="62" t="inlineStr">
         <is>
           <t>ПРИПУЩЕННЯ</t>
         </is>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" s="58" t="inlineStr">
         <is>
           <t>Взято з прикладу по локшині. Умови «Сільпо» не запитані</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="59" t="inlineStr">
         <is>
           <t>За 30 % полиця +17 %</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="55" t="inlineStr">
         <is>
           <t>«Маржа 35 %»</t>
         </is>
       </c>
-      <c r="B15" s="52" t="inlineStr">
+      <c r="B15" s="63" t="inlineStr">
         <is>
           <t>ВИЗНАЧЕННЯ</t>
         </is>
       </c>
-      <c r="C15" s="42" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>Валова націнка. Не містить ФОП, маркетингу, лістингу, списань</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>Не є чистою рентабельністю</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="44" t="inlineStr">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>Оборотність Ben's у «Сільпо»</t>
         </is>
       </c>
-      <c r="B16" s="53" t="inlineStr">
+      <c r="B16" s="64" t="inlineStr">
         <is>
           <t>НЕМАЄ ДАНИХ</t>
         </is>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="58" t="inlineStr">
         <is>
           <t>Мережа обсягів не віддає</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>Неможливо порахувати план продажів</t>
         </is>

--- a/rte-rice-analysis/RTE_Rice_Benchmark.xlsx
+++ b/rte-rice-analysis/RTE_Rice_Benchmark.xlsx
@@ -12,8 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Наша лінійка" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Канали" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4b. Формат x грамаж" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Калькулятор" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Застереження" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4c. Ритейл-аудит" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4d. Азійські бренди" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Калькулятор" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Застереження" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Бренди'!$A$4:$M$27</definedName>
@@ -33,7 +35,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,12 +120,6 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="FF717890"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="FF1E9EA6"/>
       <sz val="9"/>
@@ -134,8 +130,20 @@
       <color rgb="FF5D4B96"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFC94F7C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF717890"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -164,6 +172,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF7FCBCF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
@@ -185,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -254,15 +277,42 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -271,9 +321,6 @@
     <xf numFmtId="167" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -289,13 +336,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4472,7 +4513,7 @@
         </is>
       </c>
       <c r="C5" s="24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
@@ -4486,7 +4527,7 @@
       </c>
       <c r="F5" s="26" t="inlineStr">
         <is>
-          <t>Сільпо</t>
+          <t>Сільпо · МегаМаркет · Ultramarket. Решта 14 перевірених мереж категорії не мають</t>
         </is>
       </c>
     </row>
@@ -4905,6 +4946,864 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Що з готового рису реально стоїть у національних мережах</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Суцільна перевірка каталогів, 28.09.2026. Джерело: відкритий API zakaz.ua та sf-ecom-api.silpo.ua.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Мережа</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Що саме</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Формат</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Грн/уп.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Грн/100 г</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Тип зберігання</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Походження</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Сільпо</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Ben's Original / Uncle Ben's Express</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>пауч 220–250 г</t>
+        </is>
+      </c>
+      <c r="D5" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" s="38" t="inlineStr">
+        <is>
+          <t>90–179</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>36–81</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>Кімнатна · НАШ КОНКУРЕНТНИЙ СЕТ</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>Mars · ЄС</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>МегаМаркет · Ultramarket</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>The Local Food по-тайськи з куркою</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>лоток 350 г</t>
+        </is>
+      </c>
+      <c r="D6" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="38" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>Кімнатна · НАШ КОНКУРЕНТНИЙ СЕТ</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>Ашан</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>«Легко!» рис з овочами та курячим фрікасе</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>лоток 280 г</t>
+        </is>
+      </c>
+      <c r="D7" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="38" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>Охолоджена кулінарія · 2–5 діб</t>
+        </is>
+      </c>
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Сільпо</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>«Чіл Міл» рис паровий · рис з яйцем і овочами</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>лоток</t>
+        </is>
+      </c>
+      <c r="D8" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="38" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
+      </c>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>Охолоджена кулінарія · 2–5 діб</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>Сільпо</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Боули з рисом · теріякі · рис по-китайськи</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>кулінарія</t>
+        </is>
+      </c>
+      <c r="D9" s="39" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="38" t="inlineStr">
+        <is>
+          <t>139–439</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="inlineStr">
+        <is>
+          <t>Охолоджена кулінарія · 2–5 діб</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>NOVUS</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>«Майстри Смаку» рис з овочами</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>кулінарія</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="38" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
+      </c>
+      <c r="G10" s="41" t="inlineStr">
+        <is>
+          <t>Охолоджена кулінарія · 2–5 діб</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="38" t="inlineStr">
+        <is>
+          <t>МегаМаркет · Ultramarket</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Рис японський з овочами</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>кулінарія</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="38" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
+      </c>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>Охолоджена кулінарія · 2–5 діб</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>Ашан · NOVUS · МегаМаркет · Сільпо</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>«Жменька» Tasty Mix басматі з овочами</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>пакет 200 г</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="38" t="inlineStr">
+        <is>
+          <t>89–92</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G12" s="42" t="inlineStr">
+        <is>
+          <t>Суміш під варіння · не готовий</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>NOVUS · Сільпо</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Trapeza басматі з карі по-індійськи</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>пакет 250 г</t>
+        </is>
+      </c>
+      <c r="D13" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="38" t="inlineStr">
+        <is>
+          <t>59–85</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>24–34</t>
+        </is>
+      </c>
+      <c r="G13" s="42" t="inlineStr">
+        <is>
+          <t>Суміш під варіння · не готовий</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>МегаМаркет · Ultramarket</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>«Зерновита» рис з овочами</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>пакет 500 г</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="38" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>Суміш під варіння · не готовий</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="38" t="inlineStr">
+        <is>
+          <t>METRO</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>готового рису немає</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="43" t="inlineStr">
+        <is>
+          <t>Категорії немає</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>лише крупа 1–10 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Підсумок</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Ambient (наш конкурентний сет): 12 SKU на всю країну. 11 з них — Ben's Original у «Сільпо».</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Єдина інша ambient-позиція: The Local Food по-тайськи 350 г, 207 грн, МегаМаркет і Ultramarket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>METRO: готового рису немає взагалі — лише крупа 1–10 кг під Metro Chef і Aro для HoReCa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Фоззі Cash&amp;Carry перевірити не вдалося: каталог закритий ботозахистом. За аналогією з METRO (той самий формат C&amp;C) ambient-рису там також не очікується — це припущення, не факт.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Азійські бренди, що вже стоять у національних мережах</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>163 позиції в каталогах мереж. Жодна з них не рис.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Бренд</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Ашан</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Сільпо</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>METRO</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NOVUS</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Космос</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>З них рис</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Що саме стоїть</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Ottogi</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="32">
+        <f>SUM(B5:F5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>локшина, рамен</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Bibigo</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="32">
+        <f>SUM(B6:F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>токпокі, стір-фрай рамен</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Samyang</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="n">
+        <v>17</v>
+      </c>
+      <c r="C7" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="32">
+        <f>SUM(B7:F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Nongshim</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="44" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="32">
+        <f>SUM(B8:F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>локшина</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Paldo</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n">
+        <v>18</v>
+      </c>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="32">
+        <f>SUM(B9:F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>локшина</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Aroy-D</t>
+        </is>
+      </c>
+      <c r="B10" s="44" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="44" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" s="32">
+        <f>SUM(B10:F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>соуси, пасти, кокос</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Що це означає</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>1. Ottogi має 14 позицій у трьох мережах, Bibigo — 6 в «Ашані». Імпортер, лістинг і полиця вже існують.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>2. Ті самі Ottogi і Bibigo продають чаші з рисом по 225–356 грн — але лише в азійських фудшопах.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>3. Бар'єр входу азійського рису в мережу — не дистрибуція, а те, що ніхто цього не зробив.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>4. Ризик: імпортер Ottogi додасть рисові SKU до наявного лістингу швидше, ніж ми збудуємо свій.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4931,112 +5830,112 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>Курс, грн/$</t>
         </is>
       </c>
-      <c r="B4" s="39" t="n">
+      <c r="B4" s="48" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Бонус мережі, %</t>
         </is>
       </c>
-      <c r="B5" s="40" t="n">
+      <c r="B5" s="49" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Цільова маржа, %</t>
         </is>
       </c>
-      <c r="B6" s="40" t="n">
+      <c r="B6" s="49" t="n">
         <v>0.35</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Націнка мережі (x)</t>
         </is>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="48" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>Частка ціни для собівартості</t>
         </is>
       </c>
-      <c r="B8" s="41">
+      <c r="B8" s="50">
         <f>1-B5-B6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>Коеф. FOB → СС, 20′ FCL</t>
         </is>
       </c>
-      <c r="B9" s="42" t="n">
+      <c r="B9" s="51" t="n">
         <v>1.70740755878359</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Коеф. FOB → СС, 40′ FCL</t>
         </is>
       </c>
-      <c r="B10" s="42" t="n">
+      <c r="B10" s="51" t="n">
         <v>1.530558573152913</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Полиця = СС_грн × націнка / частка_СС</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>Множник СС → полиця</t>
         </is>
       </c>
-      <c r="B12" s="44">
+      <c r="B12" s="53">
         <f>B7/B8</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>Множник FOB → полиця, 20′ FCL</t>
         </is>
       </c>
-      <c r="B13" s="45">
+      <c r="B13" s="54">
         <f>B9*B4*B12</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>Множник FOB → полиця, 40′ FCL</t>
         </is>
       </c>
-      <c r="B14" s="45">
+      <c r="B14" s="54">
         <f>B10*B4*B12</f>
         <v/>
       </c>
@@ -5074,7 +5973,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="46" t="n">
+      <c r="A18" s="55" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -5082,51 +5981,51 @@
           <t>Ben's Original медіана 41 грн/100 г при 240 г</t>
         </is>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="56">
         <f>A18/$B$12</f>
         <v/>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="57">
         <f>C18/$B$4</f>
         <v/>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="58">
         <f>A18/$B$13</f>
         <v/>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="58">
         <f>A18/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="n">
+      <c r="A19" s="59" t="n">
         <v>109</v>
       </c>
-      <c r="B19" s="51" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>Медіана формату «пауч» — найдешевший вхід у мережу</t>
         </is>
       </c>
-      <c r="C19" s="52">
+      <c r="C19" s="61">
         <f>A19/$B$12</f>
         <v/>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="62">
         <f>C19/$B$4</f>
         <v/>
       </c>
-      <c r="E19" s="54">
+      <c r="E19" s="63">
         <f>A19/$B$13</f>
         <v/>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="63">
         <f>A19/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="n">
+      <c r="A20" s="55" t="n">
         <v>119</v>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -5134,51 +6033,51 @@
           <t>Агресивний сценарій для стакана 150 г</t>
         </is>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="56">
         <f>A20/$B$12</f>
         <v/>
       </c>
-      <c r="D20" s="48">
+      <c r="D20" s="57">
         <f>C20/$B$4</f>
         <v/>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="58">
         <f>A20/$B$13</f>
         <v/>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="58">
         <f>A20/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="n">
+      <c r="A21" s="59" t="n">
         <v>129</v>
       </c>
-      <c r="B21" s="51" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>РЕКОМЕНДОВАНО для стакана 150 г — нижче Henan-медіани</t>
         </is>
       </c>
-      <c r="C21" s="52">
+      <c r="C21" s="61">
         <f>A21/$B$12</f>
         <v/>
       </c>
-      <c r="D21" s="53">
+      <c r="D21" s="62">
         <f>C21/$B$4</f>
         <v/>
       </c>
-      <c r="E21" s="54">
+      <c r="E21" s="63">
         <f>A21/$B$13</f>
         <v/>
       </c>
-      <c r="F21" s="54">
+      <c r="F21" s="63">
         <f>A21/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="46" t="n">
+      <c r="A22" s="55" t="n">
         <v>139</v>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -5186,51 +6085,51 @@
           <t>Поточна полиця стакана 150 г без переговорів</t>
         </is>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="56">
         <f>A22/$B$12</f>
         <v/>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="57">
         <f>C22/$B$4</f>
         <v/>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="58">
         <f>A22/$B$13</f>
         <v/>
       </c>
-      <c r="F22" s="49">
+      <c r="F22" s="58">
         <f>A22/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="n">
+      <c r="A23" s="59" t="n">
         <v>155</v>
       </c>
-      <c r="B23" s="51" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>Паритет із Bibigo 210 г (135–189 грн)</t>
         </is>
       </c>
-      <c r="C23" s="52">
+      <c r="C23" s="61">
         <f>A23/$B$12</f>
         <v/>
       </c>
-      <c r="D23" s="53">
+      <c r="D23" s="62">
         <f>C23/$B$4</f>
         <v/>
       </c>
-      <c r="E23" s="54">
+      <c r="E23" s="63">
         <f>A23/$B$13</f>
         <v/>
       </c>
-      <c r="F23" s="54">
+      <c r="F23" s="63">
         <f>A23/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="46" t="n">
+      <c r="A24" s="55" t="n">
         <v>179</v>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -5238,45 +6137,45 @@
           <t>Верх вікна мережевої полиці</t>
         </is>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="56">
         <f>A24/$B$12</f>
         <v/>
       </c>
-      <c r="D24" s="48">
+      <c r="D24" s="57">
         <f>C24/$B$4</f>
         <v/>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="58">
         <f>A24/$B$13</f>
         <v/>
       </c>
-      <c r="F24" s="49">
+      <c r="F24" s="58">
         <f>A24/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="n">
+      <c r="A25" s="59" t="n">
         <v>199</v>
       </c>
-      <c r="B25" s="51" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>Ottogi −22 % — стеля для лотка ONE'S 200 г</t>
         </is>
       </c>
-      <c r="C25" s="52">
+      <c r="C25" s="61">
         <f>A25/$B$12</f>
         <v/>
       </c>
-      <c r="D25" s="53">
+      <c r="D25" s="62">
         <f>C25/$B$4</f>
         <v/>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="63">
         <f>A25/$B$13</f>
         <v/>
       </c>
-      <c r="F25" s="54">
+      <c r="F25" s="63">
         <f>A25/$B$14</f>
         <v/>
       </c>
@@ -5300,7 +6199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5352,7 +6251,7 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="55" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>Ціни конкурентів на полиці</t>
         </is>
@@ -5374,29 +6273,29 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="56" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>Формати, ваги, кількість SKU</t>
         </is>
       </c>
-      <c r="B6" s="57" t="inlineStr">
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>ФАКТ</t>
         </is>
       </c>
-      <c r="C6" s="58" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>Картки продавців. 2 позиції без маси виключено з грн/100 г</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="67" t="inlineStr">
         <is>
           <t>Незначний</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Обсяг імпорту 182 т</t>
         </is>
@@ -5418,29 +6317,29 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="56" t="inlineStr">
+      <c r="A8" s="64" t="inlineStr">
         <is>
           <t>Ємність роздрібу 87–110 млн грн</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="68" t="inlineStr">
         <is>
           <t>ОЦІНКА</t>
         </is>
       </c>
-      <c r="C8" s="58" t="inlineStr">
+      <c r="C8" s="66" t="inlineStr">
         <is>
           <t>Імпорт × 2,2–2,8. Заміряних продажів немає</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="67" t="inlineStr">
         <is>
           <t>Похибка ±30 % у бізнес-кейсі</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Собівартість BSCM і CM Premium</t>
         </is>
@@ -5462,34 +6361,34 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="56" t="inlineStr">
+      <c r="A10" s="64" t="inlineStr">
         <is>
           <t>FOB ONE'S International</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="68" t="inlineStr">
         <is>
           <t>ОЦІНКА</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>Виведено з СС за коефіцієнтом 1,7074. Постачальник FOB не розкрив</t>
         </is>
       </c>
-      <c r="D10" s="59" t="inlineStr">
+      <c r="D10" s="67" t="inlineStr">
         <is>
           <t>Рекомендація по Fried Rice 200 г може бути хибною</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="55" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Коеф. FOB → СС = 1,7074</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>РОЗРАХУНОК</t>
         </is>
@@ -5506,29 +6405,29 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="56" t="inlineStr">
+      <c r="A12" s="64" t="inlineStr">
         <is>
           <t>Мито 10 % у собівартості</t>
         </is>
       </c>
-      <c r="B12" s="62" t="inlineStr">
+      <c r="B12" s="69" t="inlineStr">
         <is>
           <t>ПРИПУЩЕННЯ</t>
         </is>
       </c>
-      <c r="C12" s="58" t="inlineStr">
+      <c r="C12" s="66" t="inlineStr">
         <is>
           <t>Зазначено в RTE_Rice_Suppliers. Первинне джерело не наведено</t>
         </is>
       </c>
-      <c r="D12" s="59" t="inlineStr">
+      <c r="D12" s="67" t="inlineStr">
         <is>
           <t>±27 грн на полиці</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>Імпортний ПДВ 20 % у СС</t>
         </is>
@@ -5550,34 +6449,34 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="56" t="inlineStr">
+      <c r="A14" s="64" t="inlineStr">
         <is>
           <t>Бонус мережі 25 %</t>
         </is>
       </c>
-      <c r="B14" s="62" t="inlineStr">
+      <c r="B14" s="69" t="inlineStr">
         <is>
           <t>ПРИПУЩЕННЯ</t>
         </is>
       </c>
-      <c r="C14" s="58" t="inlineStr">
+      <c r="C14" s="66" t="inlineStr">
         <is>
           <t>Взято з прикладу по локшині. Умови «Сільпо» не запитані</t>
         </is>
       </c>
-      <c r="D14" s="59" t="inlineStr">
+      <c r="D14" s="67" t="inlineStr">
         <is>
           <t>За 30 % полиця +17 %</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>«Маржа 35 %»</t>
         </is>
       </c>
-      <c r="B15" s="63" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>ВИЗНАЧЕННЯ</t>
         </is>
@@ -5594,22 +6493,22 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="56" t="inlineStr">
+      <c r="A16" s="64" t="inlineStr">
         <is>
           <t>Оборотність Ben's у «Сільпо»</t>
         </is>
       </c>
-      <c r="B16" s="64" t="inlineStr">
+      <c r="B16" s="70" t="inlineStr">
         <is>
           <t>НЕМАЄ ДАНИХ</t>
         </is>
       </c>
-      <c r="C16" s="58" t="inlineStr">
+      <c r="C16" s="66" t="inlineStr">
         <is>
           <t>Мережа обсягів не віддає</t>
         </is>
       </c>
-      <c r="D16" s="59" t="inlineStr">
+      <c r="D16" s="67" t="inlineStr">
         <is>
           <t>Неможливо порахувати план продажів</t>
         </is>

--- a/rte-rice-analysis/RTE_Rice_Benchmark.xlsx
+++ b/rte-rice-analysis/RTE_Rice_Benchmark.xlsx
@@ -18,7 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Застереження" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Бренди'!$A$4:$M$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. Бренди'!$A$4:$L$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Наша лінійка'!$A$4:$O$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -62,12 +62,12 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <b val="1"/>
       <color rgb="FF303A5D"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="FF303A5D"/>
       <sz val="9"/>
     </font>
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -217,26 +217,25 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -280,7 +279,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -327,7 +326,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -735,12 +734,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -748,9 +747,8 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -770,19 +768,19 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Сегмент</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Бренд</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Країна</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Технологія</t>
-        </is>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Формат</t>
@@ -820,15 +818,10 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>грн/100 г min</t>
+          <t>Що це таке</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>грн/100 г max</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Канал</t>
         </is>
@@ -837,25 +830,25 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>СЕГМЕНТ 1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
           <t>Ben's Original</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>ЄС</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Розігрів</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="4" t="n">
         <v>13</v>
       </c>
       <c r="F5" s="6" t="n">
@@ -873,13 +866,12 @@
       <c r="J5" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>81</v>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Пауч від Mars. Мікрохвильовка 90 с. Єдиний у мережевому роздрібі</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Мережа + маркетплейс</t>
         </is>
@@ -888,25 +880,25 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>СЕГМЕНТ 1</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
           <t>Маркел</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Розігрів</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="9" t="n">
@@ -924,13 +916,12 @@
       <c r="J6" s="9" t="n">
         <v>350</v>
       </c>
-      <c r="K6" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="L6" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>Український реторт для військторгу</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>Військторг</t>
         </is>
@@ -939,25 +930,25 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>СЕГМЕНТ 1</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
           <t>Portion</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Розігрів</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
@@ -975,13 +966,12 @@
       <c r="J7" s="6" t="n">
         <v>350</v>
       </c>
-      <c r="K7" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Український реторт 350 г. Найдешевший грам категорії</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Маркетплейс</t>
         </is>
@@ -990,229 +980,225 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Харчі</t>
+          <t>СЕГМЕНТ 1</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Україна</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Сублімація</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Дойпак</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>4</v>
+          <t>Bibigo</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Корея</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Чаша</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>321</v>
+        <v>189</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>98</v>
-      </c>
-      <c r="L8" s="9" t="n">
-        <v>321</v>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>Туризм</t>
+        <v>210</v>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Корейський лоток білого рису. Розігрів 90 с</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>Фудшопи + маркетплейс</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>James Cook</t>
+          <t>СЕГМЕНТ 1</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Україна</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Сублімація</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Дойпак</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>4</v>
+          <t>Ottogi</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Корея</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Чаша</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>55</v>
+        <v>225</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>156</v>
+        <v>356</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>195</v>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Туризм</t>
+        <v>320</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Корейська чаша з м'ясом і соусом. Розігрів 2 хв</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Азійські фудшопи</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>!FEST</t>
+          <t>СЕГМЕНТ 1</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Україна</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Сублімація</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Дойпак</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n">
+          <t>Clearspring</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>ЄС</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Пауч</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>133</v>
+        <v>252</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>140</v>
+        <v>446</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>137</v>
+        <v>349</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>133</v>
-      </c>
-      <c r="L10" s="9" t="n">
-        <v>140</v>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>Туризм</t>
+        <v>250</v>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Органічний пауч з ЄС. Найдорожчий пауч ринку</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>Маркетплейс + спец.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Їжа в Похід</t>
+          <t>СЕГМЕНТ 1</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Україна</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Сублімація</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Дойпак</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>2</v>
+          <t>Adventure Menu</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>ЄС</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Пауч/Дойпак</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>130</v>
+        <v>315</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>145</v>
+        <v>483</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>138</v>
+        <v>378</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>85</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>153</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>171</v>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Власний магазин</t>
+        <v>400</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Реторт 400 г + сублімат 110 г. Два формати в одному бренді</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>Туризм</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>СЕГМЕНТ 2</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
           <t>Henan</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Окріп</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F12" s="9" t="n">
@@ -1230,13 +1216,12 @@
       <c r="J12" s="9" t="n">
         <v>174</v>
       </c>
-      <c r="K12" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="L12" s="9" t="n">
-        <v>106</v>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Китайська чаша сухого рису. Залити окропом на 8 хв</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>Азійські фудшопи + МП</t>
         </is>
@@ -1245,347 +1230,348 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Bibigo</t>
+          <t>СЕГМЕНТ 2</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Корея</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Розігрів</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+          <t>Gallina Blanca</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>ЄС</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
+      <c r="E13" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>135</v>
+        <v>229</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>210</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>Фудшопи + маркетплейс</t>
+        <v>84</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Іспанський інстант-рис у чаші 84 г. Окріп</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Спец. магазин</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Gallina Blanca</t>
+          <t>СЕГМЕНТ 2</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>ЄС</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Окріп</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Чаша</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="n">
+          <t>Qiaoshanmei</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Китай</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Пакет</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>229</v>
+        <v>501</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>229</v>
+        <v>501</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>229</v>
+        <v>501</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>84</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>273</v>
-      </c>
-      <c r="L14" s="9" t="n">
-        <v>273</v>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t>Спец. магазин</t>
+        <v>146</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Китайський рис у пакеті під окріп</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>Азійський фудшоп</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Ottogi</t>
+          <t>СЕГМЕНТ 3</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Корея</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Розігрів</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Чаша</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
+          <t>Haidilao</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Китай</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Коробка</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>225</v>
+        <v>380</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>356</v>
+        <v>1190</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>255</v>
+        <v>680</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>217</v>
+        <v>165</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>130</v>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Азійські фудшопи</t>
+        <v>360</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Коробка з хімічним нагрівачем. Готується без техніки</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>Туризм + фудшопи</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>SubliMate</t>
+          <t>СЕГМЕНТ 3</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Україна</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Сублімація</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Дойпак</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>3</v>
+          <t>Zihaiguo</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Китай</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Коробка</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>290</v>
+        <v>735</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>370</v>
+        <v>735</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>310</v>
+        <v>735</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>110</v>
+        <v>440</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>140</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>221</v>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>308</v>
-      </c>
-      <c r="M16" s="8" t="inlineStr">
-        <is>
-          <t>Туризм</t>
+        <v>440</v>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Коробка-саморозігрів 440 г</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>Азійський фудшоп</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Clearspring</t>
+          <t>СЕГМЕНТ 3</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>ЄС</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Розігрів</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Пауч</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
+          <t>Rongcheng Haoji</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Китай</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Коробка</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>252</v>
+        <v>735</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>446</v>
+        <v>735</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>349</v>
+        <v>735</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>250</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>101</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>178</v>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Маркетплейс + спец.</t>
+        <v>440</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Коробка-саморозігрів 440 г</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>Азійський фудшоп</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Adventure Menu</t>
+          <t>СЕГМЕНТ 3</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>ЄС</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Розігрів+Субл.</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Пауч/Дойпак</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>5</v>
+          <t>Mo Xiao Xian</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Китай</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Чаша</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>315</v>
+        <v>931</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>483</v>
+        <v>931</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>378</v>
+        <v>931</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>400</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="L18" s="9" t="n">
-        <v>439</v>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>Туризм</t>
+        <v>275</v>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Китайська чаша-саморозігрів. Найдорожча чаша ринку</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Азійський фудшоп</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Trek'n Eat</t>
+          <t>СЕГМЕНТ 4</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>ЄС</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Сублімація</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
+          <t>Харчі</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Дойпак</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>2</v>
+      <c r="E19" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>269</v>
+        <v>83</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>715</v>
+        <v>321</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>492</v>
-      </c>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
-      <c r="M19" s="5" t="inlineStr">
+        <v>120</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Український сублімат для туризму й армії</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Туризм</t>
         </is>
@@ -1594,49 +1580,48 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Adventure Food</t>
+          <t>СЕГМЕНТ 4</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>ЄС</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Сублімація</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
+          <t>James Cook</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Дойпак</t>
         </is>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>1</v>
+      <c r="E20" s="7" t="n">
+        <v>4</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>492</v>
+        <v>55</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>492</v>
+        <v>156</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>492</v>
+        <v>133</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>146</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>337</v>
-      </c>
-      <c r="L20" s="9" t="n">
-        <v>337</v>
-      </c>
-      <c r="M20" s="8" t="inlineStr">
+        <v>90</v>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Український сублімат. Найширша вітчизняна лінійка</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>Туризм</t>
         </is>
@@ -1645,202 +1630,194 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Qiaoshanmei</t>
+          <t>СЕГМЕНТ 4</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Окріп</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Пакет</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>2</v>
+          <t>!FEST</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Дойпак</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>501</v>
+        <v>133</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>501</v>
+        <v>140</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>501</v>
+        <v>137</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>146</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>343</v>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>343</v>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>Азійський фудшоп</t>
+        <v>100</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Український сублімат, львівський бренд</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Туризм</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Travellunch</t>
+          <t>СЕГМЕНТ 4</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>ЄС</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Сублімація</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+          <t>Їжа в Похід</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Дойпак</t>
         </is>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>7</v>
+      <c r="E22" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>275</v>
+        <v>130</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>889</v>
+        <v>145</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>515</v>
+        <v>138</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>250</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>220</v>
-      </c>
-      <c r="L22" s="9" t="n">
-        <v>454</v>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>Туризм</t>
+        <v>85</v>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Український сублімат, власний магазин</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Власний магазин</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Haidilao</t>
+          <t>СЕГМЕНТ 4</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Саморозігрів</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Коробка</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>10</v>
+          <t>SubliMate</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Україна</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Дойпак</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>380</v>
+        <v>290</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1190</v>
+        <v>370</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>680</v>
+        <v>310</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>360</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>230</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>371</v>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>Туризм + фудшопи</t>
+        <v>140</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Український сублімат</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Туризм</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Mountain House</t>
+          <t>СЕГМЕНТ 4</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>США</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Сублімація</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
+          <t>Trek'n Eat</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>ЄС</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Дойпак</t>
         </is>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>699</v>
+        <v>269</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>699</v>
+        <v>715</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>699</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>110</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>133</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>526</v>
-      </c>
-      <c r="L24" s="9" t="n">
-        <v>635</v>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
+        <v>492</v>
+      </c>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Німецький сублімат для туризму</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>Туризм</t>
         </is>
@@ -1849,158 +1826,155 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Zihaiguo</t>
+          <t>СЕГМЕНТ 4</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Саморозігрів</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Коробка</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n">
+          <t>Adventure Food</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>ЄС</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Дойпак</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>735</v>
+        <v>492</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>735</v>
+        <v>492</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>735</v>
+        <v>492</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>440</v>
+        <v>146</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>440</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>167</v>
-      </c>
-      <c r="L25" s="6" t="n">
-        <v>167</v>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Азійський фудшоп</t>
+        <v>146</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Нідерландський сублімат</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Туризм</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Rongcheng Haoji</t>
+          <t>СЕГМЕНТ 4</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Саморозігрів</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Коробка</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>1</v>
+          <t>Travellunch</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>ЄС</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Дойпак</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>735</v>
+        <v>275</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>735</v>
+        <v>889</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>735</v>
+        <v>515</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>440</v>
+        <v>125</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>440</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>167</v>
-      </c>
-      <c r="L26" s="9" t="n">
-        <v>167</v>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>Азійський фудшоп</t>
+        <v>250</v>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Німецький сублімат. Найширша імпортна лінійка</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Туризм</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Mo Xiao Xian</t>
+          <t>СЕГМЕНТ 4</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Саморозігрів</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Чаша</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
+          <t>Mountain House</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>США</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Дойпак</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>931</v>
+        <v>699</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>931</v>
+        <v>699</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>931</v>
+        <v>699</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>275</v>
+        <v>110</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>275</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>339</v>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>339</v>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Азійський фудшоп</t>
+        <v>133</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Американський сублімат. Найдорожчий грам категорії</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Туризм</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M27"/>
+  <autoFilter ref="A4:L27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2011,7 +1985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2022,8 +1996,7 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="56" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -2083,11 +2056,6 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>грн/100 г</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
           <t>Коментар</t>
         </is>
       </c>
@@ -2119,11 +2087,7 @@
       <c r="H5" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="I5" s="12">
-        <f>E5/H5*100</f>
-        <v/>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Формат мережевої полиці. Найнижча ціна входу в категорію.</t>
         </is>
@@ -2156,11 +2120,7 @@
       <c r="H6" s="6" t="n">
         <v>218</v>
       </c>
-      <c r="I6" s="12">
-        <f>E6/H6*100</f>
-        <v/>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Формат азійського каналу. Прямі конкуренти Ottogi і Henan.</t>
         </is>
@@ -2193,11 +2153,7 @@
       <c r="H7" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="I7" s="12">
-        <f>E7/H7*100</f>
-        <v/>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>Формат туристичного каналу. Потребує окропу, не полиця.</t>
         </is>
@@ -2230,25 +2186,21 @@
       <c r="H8" s="6" t="n">
         <v>230</v>
       </c>
-      <c r="I8" s="12">
-        <f>E8/H8*100</f>
-        <v/>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>Найдорожчий формат. Купується як подарунок або в дорогу.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Висновок</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Дойпак лідирує за кількістю позицій (36 %), але це артефакт туристичного каналу. За ціною для покупця виграє пауч: 109 грн проти 315 грн.</t>
         </is>
@@ -2282,7 +2234,6 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -2362,27 +2313,22 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>грн/100 г</t>
+          <t>Ринковий орієнтир</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>Ринковий орієнтир</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
           <t>Позиція</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>BSCM — пауч 240 г</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Jasmine Rice</t>
         </is>
@@ -2390,35 +2336,35 @@
       <c r="C5" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="15" t="n">
         <v>0.995418606770833</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="15" t="n">
         <v>0.892315648148148</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="16">
         <f>F5*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="16">
         <f>H5/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="16">
         <f>I5*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K5" s="18">
+      <c r="K5" s="17">
         <f>I5*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -2426,27 +2372,27 @@
         <f>G5*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M5" s="18">
+      <c r="M5" s="17">
         <f>K5/C5*100</f>
         <v/>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="4">
         <f>IF(K5&lt;=180,IF(K5&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>BSCM — пауч 240 г</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Mexican Rice</t>
         </is>
@@ -2454,35 +2400,35 @@
       <c r="C6" s="9" t="n">
         <v>240</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="18" t="n">
         <v>1.13762102083333</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="18" t="n">
         <v>1.0197892037037</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <f>F6*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="19">
         <f>H6/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="19">
         <f>I6*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="20">
         <f>I6*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -2490,27 +2436,27 @@
         <f>G6*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M6" s="21">
+      <c r="M6" s="20">
         <f>K6/C6*100</f>
         <v/>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="7">
         <f>IF(K6&lt;=180,IF(K6&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>BSCM — пауч 240 г</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Japanese Style Rice</t>
         </is>
@@ -2518,35 +2464,35 @@
       <c r="C7" s="6" t="n">
         <v>240</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="15" t="n">
         <v>1.13762102083333</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="15" t="n">
         <v>1.0197892037037</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="16">
         <f>F7*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="16">
         <f>H7/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <f>I7*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K7" s="18">
+      <c r="K7" s="17">
         <f>I7*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -2554,27 +2500,27 @@
         <f>G7*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M7" s="18">
+      <c r="M7" s="17">
         <f>K7/C7*100</f>
         <v/>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="4">
         <f>IF(K7&lt;=180,IF(K7&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>BSCM — пауч 240 г</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Hot and Spicy Rice</t>
         </is>
@@ -2582,35 +2528,35 @@
       <c r="C8" s="9" t="n">
         <v>240</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <v>1.27982343489583</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="18" t="n">
         <v>1.14726275925926</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="19">
         <f>F8*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="19">
         <f>H8/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="19">
         <f>I8*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="20">
         <f>I8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -2618,27 +2564,27 @@
         <f>G8*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M8" s="21">
+      <c r="M8" s="20">
         <f>K8/C8*100</f>
         <v/>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="7" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="7">
         <f>IF(K8&lt;=180,IF(K8&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>BSCM — пауч 200 г</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Jasmine Rice (Pathum)</t>
         </is>
@@ -2646,35 +2592,35 @@
       <c r="C9" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="15" t="n">
         <v>0.952556220056099</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="15" t="n">
         <v>0.846095788605277</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="16">
         <f>F9*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="16">
         <f>H9/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="16">
         <f>I9*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K9" s="18">
+      <c r="K9" s="17">
         <f>I9*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -2682,27 +2628,27 @@
         <f>G9*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="17">
         <f>K9/C9*100</f>
         <v/>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="4">
         <f>IF(K9&lt;=180,IF(K9&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>BSCM — пауч 200 г</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Mexican Rice</t>
         </is>
@@ -2710,35 +2656,35 @@
       <c r="C10" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <v>1.07379043215039</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="18" t="n">
         <v>0.953780613255561</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="19">
         <f>F10*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="19">
         <f>H10/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="19">
         <f>I10*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="20">
         <f>I10*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -2746,27 +2692,27 @@
         <f>G10*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M10" s="21">
+      <c r="M10" s="20">
         <f>K10/C10*100</f>
         <v/>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="7">
         <f>IF(K10&lt;=180,IF(K10&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>BSCM — пауч 200 г</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Japanese Style Rice</t>
         </is>
@@ -2774,35 +2720,35 @@
       <c r="C11" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="15" t="n">
         <v>1.07379043215039</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="15" t="n">
         <v>0.953780613255561</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="16">
         <f>F11*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="16">
         <f>H11/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="16">
         <f>I11*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="17">
         <f>I11*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -2810,27 +2756,27 @@
         <f>G11*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M11" s="18">
+      <c r="M11" s="17">
         <f>K11/C11*100</f>
         <v/>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O11" s="5">
+      <c r="O11" s="4">
         <f>IF(K11&lt;=180,IF(K11&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>BSCM — пауч 200 г</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Hot and Spicy Rice</t>
         </is>
@@ -2838,35 +2784,35 @@
       <c r="C12" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="18" t="n">
         <v>1.17770547108835</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="18" t="n">
         <v>1.04608189152723</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="19">
         <f>F12*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="19">
         <f>H12/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="19">
         <f>I12*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="20">
         <f>I12*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -2874,27 +2820,27 @@
         <f>G12*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M12" s="21">
+      <c r="M12" s="20">
         <f>K12/C12*100</f>
         <v/>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="7" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="7">
         <f>IF(K12&lt;=180,IF(K12&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>BSCM — пауч 150 г</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Jasmine Rice (Pathum)</t>
         </is>
@@ -2902,35 +2848,35 @@
       <c r="C13" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="15" t="n">
         <v>0.842849973738682</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="15" t="n">
         <v>0.7388664317893781</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="16">
         <f>F13*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="16">
         <f>H13/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="16">
         <f>I13*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="17">
         <f>I13*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -2938,27 +2884,27 @@
         <f>G13*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M13" s="18">
+      <c r="M13" s="17">
         <f>K13/C13*100</f>
         <v/>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O13" s="5">
+      <c r="O13" s="4">
         <f>IF(K13&lt;=180,IF(K13&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>BSCM — пауч 150 г</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Mexican Rice</t>
         </is>
@@ -2966,35 +2912,35 @@
       <c r="C14" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <v>0.981094929271472</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="18" t="n">
         <v>0.860056042975836</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="19">
         <f>F14*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="19">
         <f>H14/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="19">
         <f>I14*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K14" s="21">
+      <c r="K14" s="20">
         <f>I14*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3002,27 +2948,27 @@
         <f>G14*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M14" s="21">
+      <c r="M14" s="20">
         <f>K14/C14*100</f>
         <v/>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="7">
         <f>IF(K14&lt;=180,IF(K14&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>BSCM — пауч 150 г</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Japanese Style Rice</t>
         </is>
@@ -3030,35 +2976,35 @@
       <c r="C15" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="15" t="n">
         <v>0.981094929271472</v>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="15" t="n">
         <v>0.860056042975836</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="16">
         <f>F15*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="16">
         <f>H15/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="16">
         <f>I15*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K15" s="18">
+      <c r="K15" s="17">
         <f>I15*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3066,27 +3012,27 @@
         <f>G15*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M15" s="18">
+      <c r="M15" s="17">
         <f>K15/C15*100</f>
         <v/>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O15" s="5">
+      <c r="O15" s="4">
         <f>IF(K15&lt;=180,IF(K15&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>BSCM — пауч 150 г</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Hot and Spicy Rice</t>
         </is>
@@ -3094,35 +3040,35 @@
       <c r="C16" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="18" t="n">
         <v>1.07028522316359</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="18" t="n">
         <v>0.938242888902583</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="19">
         <f>F16*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="19">
         <f>H16/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="19">
         <f>I16*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K16" s="21">
+      <c r="K16" s="20">
         <f>I16*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3130,27 +3076,27 @@
         <f>G16*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M16" s="21">
+      <c r="M16" s="20">
         <f>K16/C16*100</f>
         <v/>
       </c>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O16" s="8">
+      <c r="O16" s="7">
         <f>IF(K16&lt;=180,IF(K16&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>BSCM — стакан 150 г</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Thai Jasmine Rice</t>
         </is>
@@ -3158,35 +3104,35 @@
       <c r="C17" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="15" t="n">
         <v>0.881437262584171</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="15" t="n">
         <v>0.776655999619468</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="16">
         <f>F17*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="16">
         <f>H17/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="16">
         <f>I17*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K17" s="18">
+      <c r="K17" s="17">
         <f>I17*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3194,27 +3140,27 @@
         <f>G17*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M17" s="18">
+      <c r="M17" s="17">
         <f>K17/C17*100</f>
         <v/>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O17" s="5">
+      <c r="O17" s="4">
         <f>IF(K17&lt;=180,IF(K17&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>BSCM — стакан 150 г</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Thai Brown Jasmine Rice</t>
         </is>
@@ -3222,35 +3168,35 @@
       <c r="C18" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="18" t="n">
         <v>0.8814078592565751</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="18" t="n">
         <v>0.776655999619468</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="19">
         <f>F18*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="19">
         <f>H18/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="19">
         <f>I18*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K18" s="21">
+      <c r="K18" s="20">
         <f>I18*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3258,27 +3204,27 @@
         <f>G18*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M18" s="21">
+      <c r="M18" s="20">
         <f>K18/C18*100</f>
         <v/>
       </c>
-      <c r="N18" s="8" t="inlineStr">
+      <c r="N18" s="7" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="7">
         <f>IF(K18&lt;=180,IF(K18&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>BSCM — стакан 150 г</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Thai Red Jasmine Rice</t>
         </is>
@@ -3286,35 +3232,35 @@
       <c r="C19" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="15" t="n">
         <v>0.954858269166893</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="15" t="n">
         <v>0.841377226443071</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="16">
         <f>F19*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="16">
         <f>H19/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="16">
         <f>I19*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K19" s="18">
+      <c r="K19" s="17">
         <f>I19*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3322,27 +3268,27 @@
         <f>G19*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M19" s="18">
+      <c r="M19" s="17">
         <f>K19/C19*100</f>
         <v/>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O19" s="5">
+      <c r="O19" s="4">
         <f>IF(K19&lt;=180,IF(K19&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>BSCM — стакан 150 г</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Rice Berry</t>
         </is>
@@ -3350,35 +3296,35 @@
       <c r="C20" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="18" t="n">
         <v>0.954858269166893</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G20" s="18" t="n">
         <v>0.841377226443071</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="19">
         <f>F20*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="19">
         <f>H20/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="19">
         <f>I20*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K20" s="21">
+      <c r="K20" s="20">
         <f>I20*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3386,27 +3332,27 @@
         <f>G20*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M20" s="21">
+      <c r="M20" s="20">
         <f>K20/C20*100</f>
         <v/>
       </c>
-      <c r="N20" s="8" t="inlineStr">
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O20" s="8">
+      <c r="O20" s="7">
         <f>IF(K20&lt;=180,IF(K20&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>BSCM — стакан 150 г</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Brown Jasmine + Red Quinoa</t>
         </is>
@@ -3414,35 +3360,35 @@
       <c r="C21" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="15" t="n">
         <v>0.954858269166893</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="15" t="n">
         <v>0.841377226443071</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="16">
         <f>F21*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="16">
         <f>H21/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="16">
         <f>I21*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K21" s="18">
+      <c r="K21" s="17">
         <f>I21*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3450,27 +3396,27 @@
         <f>G21*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M21" s="18">
+      <c r="M21" s="17">
         <f>K21/C21*100</f>
         <v/>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O21" s="5">
+      <c r="O21" s="4">
         <f>IF(K21&lt;=180,IF(K21&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>BSCM — подвійний стакан 2×125 г</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Jasmine Rice без олії</t>
         </is>
@@ -3478,35 +3424,35 @@
       <c r="C22" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="18" t="n">
         <v>1.6275694066699</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G22" s="18" t="n">
         <v>1.43357202931587</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="19">
         <f>F22*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I22" s="20">
+      <c r="I22" s="19">
         <f>H22/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J22" s="20">
+      <c r="J22" s="19">
         <f>I22*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K22" s="21">
+      <c r="K22" s="20">
         <f>I22*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3514,27 +3460,27 @@
         <f>G22*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M22" s="21">
+      <c r="M22" s="20">
         <f>K22/C22*100</f>
         <v/>
       </c>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O22" s="8">
+      <c r="O22" s="7">
         <f>IF(K22&lt;=180,IF(K22&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>BSCM — подвійний стакан 2×125 г</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Jasmine Rice з олією</t>
         </is>
@@ -3542,35 +3488,35 @@
       <c r="C23" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="15" t="n">
         <v>1.6275694066699</v>
       </c>
-      <c r="G23" s="16" t="n">
+      <c r="G23" s="15" t="n">
         <v>1.43357202931587</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="16">
         <f>F23*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="16">
         <f>H23/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="16">
         <f>I23*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K23" s="18">
+      <c r="K23" s="17">
         <f>I23*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3578,27 +3524,27 @@
         <f>G23*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M23" s="18">
+      <c r="M23" s="17">
         <f>K23/C23*100</f>
         <v/>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O23" s="5">
+      <c r="O23" s="4">
         <f>IF(K23&lt;=180,IF(K23&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>BSCM — подвійний стакан 2×125 г</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Jasmine (Pathum) з олією</t>
         </is>
@@ -3606,35 +3552,35 @@
       <c r="C24" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="18" t="n">
         <v>1.47960898899142</v>
       </c>
-      <c r="G24" s="19" t="n">
+      <c r="G24" s="18" t="n">
         <v>1.30324749350685</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="19">
         <f>F24*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="19">
         <f>H24/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="19">
         <f>I24*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K24" s="21">
+      <c r="K24" s="20">
         <f>I24*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3642,27 +3588,27 @@
         <f>G24*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M24" s="21">
+      <c r="M24" s="20">
         <f>K24/C24*100</f>
         <v/>
       </c>
-      <c r="N24" s="8" t="inlineStr">
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O24" s="8">
+      <c r="O24" s="7">
         <f>IF(K24&lt;=180,IF(K24&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>BSCM — подвійний стакан 2×125 г</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Brown Jasmine з олією</t>
         </is>
@@ -3670,35 +3616,35 @@
       <c r="C25" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="F25" s="15" t="n">
         <v>1.6275694066699</v>
       </c>
-      <c r="G25" s="16" t="n">
+      <c r="G25" s="15" t="n">
         <v>1.43357202931587</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="16">
         <f>F25*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="16">
         <f>H25/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="16">
         <f>I25*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K25" s="18">
+      <c r="K25" s="17">
         <f>I25*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3706,27 +3652,27 @@
         <f>G25*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M25" s="18">
+      <c r="M25" s="17">
         <f>K25/C25*100</f>
         <v/>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O25" s="5">
+      <c r="O25" s="4">
         <f>IF(K25&lt;=180,IF(K25&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>BSCM — подвійний стакан 2×125 г</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Brown Rice з олією</t>
         </is>
@@ -3734,35 +3680,35 @@
       <c r="C26" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="18" t="n">
         <v>1.62761752873563</v>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="18" t="n">
         <v>1.43357202931587</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="19">
         <f>F26*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="19">
         <f>H26/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J26" s="20">
+      <c r="J26" s="19">
         <f>I26*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K26" s="21">
+      <c r="K26" s="20">
         <f>I26*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3770,27 +3716,27 @@
         <f>G26*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M26" s="21">
+      <c r="M26" s="20">
         <f>K26/C26*100</f>
         <v/>
       </c>
-      <c r="N26" s="8" t="inlineStr">
+      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O26" s="8">
+      <c r="O26" s="7">
         <f>IF(K26&lt;=180,IF(K26&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>BSCM — подвійний стакан 2×125 г</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Basmati Rice з олією</t>
         </is>
@@ -3798,35 +3744,35 @@
       <c r="C27" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="15" t="n">
         <v>1.77552982434839</v>
       </c>
-      <c r="G27" s="16" t="n">
+      <c r="G27" s="15" t="n">
         <v>1.56389656512489</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="16">
         <f>F27*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="16">
         <f>H27/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J27" s="17">
+      <c r="J27" s="16">
         <f>I27*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K27" s="18">
+      <c r="K27" s="17">
         <f>I27*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3834,27 +3780,27 @@
         <f>G27*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M27" s="18">
+      <c r="M27" s="17">
         <f>K27/C27*100</f>
         <v/>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O27" s="5">
+      <c r="O27" s="4">
         <f>IF(K27&lt;=180,IF(K27&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>BSCM — подвійний стакан 2×125 г</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Long Grain Rice з олією</t>
         </is>
@@ -3862,35 +3808,35 @@
       <c r="C28" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>BSCM</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Чаша</t>
         </is>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="18" t="n">
         <v>1.39083273838433</v>
       </c>
-      <c r="G28" s="19" t="n">
+      <c r="G28" s="18" t="n">
         <v>1.22505277202144</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="19">
         <f>F28*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I28" s="20">
+      <c r="I28" s="19">
         <f>H28/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="19">
         <f>I28*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K28" s="21">
+      <c r="K28" s="20">
         <f>I28*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3898,27 +3844,27 @@
         <f>G28*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M28" s="21">
+      <c r="M28" s="20">
         <f>K28/C28*100</f>
         <v/>
       </c>
-      <c r="N28" s="8" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>Ottogi 225–356 · Henan 83–156</t>
         </is>
       </c>
-      <c r="O28" s="8">
+      <c r="O28" s="7">
         <f>IF(K28&lt;=180,IF(K28&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>CM Premium — пауч 250 г органік</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Organic Garlic Fried Rice</t>
         </is>
@@ -3926,35 +3872,35 @@
       <c r="C29" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>CM Premium</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="15" t="n">
         <v>1.13300100081699</v>
       </c>
-      <c r="G29" s="16" t="n">
+      <c r="G29" s="15" t="n">
         <v>1.01722856884058</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="16">
         <f>F29*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="16">
         <f>H29/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J29" s="17">
+      <c r="J29" s="16">
         <f>I29*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K29" s="18">
+      <c r="K29" s="17">
         <f>I29*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -3962,27 +3908,27 @@
         <f>G29*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M29" s="18">
+      <c r="M29" s="17">
         <f>K29/C29*100</f>
         <v/>
       </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O29" s="5">
+      <c r="O29" s="4">
         <f>IF(K29&lt;=180,IF(K29&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>CM Premium — пауч 250 г органік</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Organic Cilantro Lime Rice</t>
         </is>
@@ -3990,35 +3936,35 @@
       <c r="C30" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>CM Premium</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="18" t="n">
         <v>1.13300100081699</v>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G30" s="18" t="n">
         <v>1.01722856884058</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="19">
         <f>F30*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="19">
         <f>H30/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="19">
         <f>I30*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K30" s="21">
+      <c r="K30" s="20">
         <f>I30*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -4026,27 +3972,27 @@
         <f>G30*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M30" s="21">
+      <c r="M30" s="20">
         <f>K30/C30*100</f>
         <v/>
       </c>
-      <c r="N30" s="8" t="inlineStr">
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O30" s="8">
+      <c r="O30" s="7">
         <f>IF(K30&lt;=180,IF(K30&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>CM Premium — пауч 250 г органік</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Organic Turmeric Basmati</t>
         </is>
@@ -4054,35 +4000,35 @@
       <c r="C31" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>CM Premium</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="15" t="n">
         <v>1.13300100081699</v>
       </c>
-      <c r="G31" s="16" t="n">
+      <c r="G31" s="15" t="n">
         <v>1.01722856884058</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <f>F31*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <f>H31/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J31" s="17">
+      <c r="J31" s="16">
         <f>I31*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K31" s="18">
+      <c r="K31" s="17">
         <f>I31*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -4090,27 +4036,27 @@
         <f>G31*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M31" s="18">
+      <c r="M31" s="17">
         <f>K31/C31*100</f>
         <v/>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O31" s="5">
+      <c r="O31" s="4">
         <f>IF(K31&lt;=180,IF(K31&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>CM Premium — пауч 250 г органік</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Organic Jasmine Rice</t>
         </is>
@@ -4118,35 +4064,35 @@
       <c r="C32" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>CM Premium</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>Пауч</t>
         </is>
       </c>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="18" t="n">
         <v>1.13300100081699</v>
       </c>
-      <c r="G32" s="19" t="n">
+      <c r="G32" s="18" t="n">
         <v>1.01722856884058</v>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="19">
         <f>F32*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="19">
         <f>H32/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J32" s="20">
+      <c r="J32" s="19">
         <f>I32*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K32" s="21">
+      <c r="K32" s="20">
         <f>I32*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -4154,27 +4100,27 @@
         <f>G32*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M32" s="21">
+      <c r="M32" s="20">
         <f>K32/C32*100</f>
         <v/>
       </c>
-      <c r="N32" s="8" t="inlineStr">
+      <c r="N32" s="7" t="inlineStr">
         <is>
           <t>Ben's 45–179 · медіана 90</t>
         </is>
       </c>
-      <c r="O32" s="8">
+      <c r="O32" s="7">
         <f>IF(K32&lt;=180,IF(K32&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>ONE'S / KBROS — лоток</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Kimchi Fried Rice</t>
         </is>
@@ -4182,35 +4128,35 @@
       <c r="C33" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>ONE'S</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Лоток</t>
         </is>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="15" t="n">
         <v>2.1048630417902</v>
       </c>
-      <c r="G33" s="16" t="n">
+      <c r="G33" s="15" t="n">
         <v>1.93915406938722</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="16">
         <f>F33*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I33" s="17">
+      <c r="I33" s="16">
         <f>H33/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J33" s="17">
+      <c r="J33" s="16">
         <f>I33*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K33" s="18">
+      <c r="K33" s="17">
         <f>I33*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -4218,27 +4164,27 @@
         <f>G33*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M33" s="18">
+      <c r="M33" s="17">
         <f>K33/C33*100</f>
         <v/>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>Bibigo 135–189</t>
         </is>
       </c>
-      <c r="O33" s="5">
+      <c r="O33" s="4">
         <f>IF(K33&lt;=180,IF(K33&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>ONE'S / KBROS — лоток</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Vegetable Fried Rice</t>
         </is>
@@ -4246,35 +4192,35 @@
       <c r="C34" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>ONE'S</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>Лоток</t>
         </is>
       </c>
-      <c r="F34" s="19" t="n">
+      <c r="F34" s="18" t="n">
         <v>2.1048630417902</v>
       </c>
-      <c r="G34" s="19" t="n">
+      <c r="G34" s="18" t="n">
         <v>1.93915406938722</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="19">
         <f>F34*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I34" s="20">
+      <c r="I34" s="19">
         <f>H34/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J34" s="20">
+      <c r="J34" s="19">
         <f>I34*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K34" s="21">
+      <c r="K34" s="20">
         <f>I34*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -4282,27 +4228,27 @@
         <f>G34*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M34" s="21">
+      <c r="M34" s="20">
         <f>K34/C34*100</f>
         <v/>
       </c>
-      <c r="N34" s="8" t="inlineStr">
+      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>Bibigo 135–189</t>
         </is>
       </c>
-      <c r="O34" s="8">
+      <c r="O34" s="7">
         <f>IF(K34&lt;=180,IF(K34&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>ONE'S / KBROS — лоток</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Japchae Fried Rice</t>
         </is>
@@ -4310,35 +4256,35 @@
       <c r="C35" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>ONE'S</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Лоток</t>
         </is>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="15" t="n">
         <v>2.1048630417902</v>
       </c>
-      <c r="G35" s="16" t="n">
+      <c r="G35" s="15" t="n">
         <v>1.93915406938722</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="16">
         <f>F35*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I35" s="17">
+      <c r="I35" s="16">
         <f>H35/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J35" s="17">
+      <c r="J35" s="16">
         <f>I35*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K35" s="18">
+      <c r="K35" s="17">
         <f>I35*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -4346,27 +4292,27 @@
         <f>G35*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M35" s="18">
+      <c r="M35" s="17">
         <f>K35/C35*100</f>
         <v/>
       </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>Bibigo 135–189</t>
         </is>
       </c>
-      <c r="O35" s="5">
+      <c r="O35" s="4">
         <f>IF(K35&lt;=180,IF(K35&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>ONE'S / KBROS — лоток</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Cooked White Rice</t>
         </is>
@@ -4374,35 +4320,35 @@
       <c r="C36" s="9" t="n">
         <v>210</v>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>ONE'S</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Лоток</t>
         </is>
       </c>
-      <c r="F36" s="19" t="n">
+      <c r="F36" s="18" t="n">
         <v>0.971476418890301</v>
       </c>
-      <c r="G36" s="19" t="n">
+      <c r="G36" s="18" t="n">
         <v>0.894994727290563</v>
       </c>
-      <c r="H36" s="20">
+      <c r="H36" s="19">
         <f>F36*'5. Калькулятор'!$B$4</f>
         <v/>
       </c>
-      <c r="I36" s="20">
+      <c r="I36" s="19">
         <f>H36/'5. Калькулятор'!$B$8</f>
         <v/>
       </c>
-      <c r="J36" s="20">
+      <c r="J36" s="19">
         <f>I36*'5. Калькулятор'!$B$5</f>
         <v/>
       </c>
-      <c r="K36" s="21">
+      <c r="K36" s="20">
         <f>I36*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
@@ -4410,16 +4356,16 @@
         <f>G36*'5. Калькулятор'!$B$4/'5. Калькулятор'!$B$8*'5. Калькулятор'!$B$7</f>
         <v/>
       </c>
-      <c r="M36" s="21">
+      <c r="M36" s="20">
         <f>K36/C36*100</f>
         <v/>
       </c>
-      <c r="N36" s="8" t="inlineStr">
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>Bibigo 135–189</t>
         </is>
       </c>
-      <c r="O36" s="8">
+      <c r="O36" s="7">
         <f>IF(K36&lt;=180,IF(K36&lt;=109,"у низу вікна полиці","у вікні полиці 45–180"),"вище вікна полиці")</f>
         <v/>
       </c>
@@ -4502,127 +4448,127 @@
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Продуктовий роздріб</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Мережі національного покриття</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Масовий покупець · щоденне харчування</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>ЦІЛЬОВИЙ КАНАЛ</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Сільпо · МегаМаркет · Ultramarket. Решта 14 перевірених мереж категорії не мають</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Онлайн-маркетплейси</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Універсальні майданчики</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>Масовий покупець · плановане замовлення</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>ЦІЛЬОВИЙ КАНАЛ</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>MAUDAU · Rozetka · Prom</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Спеціалізований фудрітейл</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Азійські та етнічні магазини</t>
         </is>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Покупець азійської кухні · знає категорію</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>ЦІЛЬОВИЙ КАНАЛ · ВХІД</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>Смак Кореї · Тайякі Март · Pulsar · Апетітаріум · Gurmissimo · Edison Lee · OMG! Asia · СНЕКІС · DCM · Скарби Азії · AsiaStyle · ASIA FOODS · Wèi Māo · AsianFoods · Asia Goods Store · SushiPovar · KladezGroup · Sweet Svitt · Товари з Іспанії · Asia Foods Trade</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Outdoor- і мілітарі-рітейл</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Туристичні та військові магазини</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Турист і військовий · автономне харчування</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>НЕ НАШ ПОКУПЕЦЬ</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>ALANTUR · Highlander · ForCamp · Гайдамака · Freeride · MK-Sport · Daruy · Tactico · Лєєр · Activity та ще ~30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Мережі без жодної позиції категорії</t>
         </is>
@@ -4636,7 +4582,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Агрегатори (у підрахунок точок продажу не входять)</t>
         </is>
@@ -4736,200 +4682,200 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Пауч · реторт</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n"/>
-      <c r="C5" s="29" t="n"/>
-      <c r="D5" s="29" t="n"/>
-      <c r="E5" s="30" t="n">
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="30" t="n">
+      <c r="F5" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="29" t="n"/>
-      <c r="H5" s="31" t="n">
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="31">
         <f>SUM(B5:H5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Чаша · стакан</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="31" t="n">
+      <c r="G6" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="29" t="n"/>
-      <c r="I6" s="32">
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="31">
         <f>SUM(B6:H6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Дойпак · сублімат</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="29" t="n">
         <v>16</v>
       </c>
-      <c r="D7" s="29" t="n"/>
-      <c r="E7" s="29" t="n"/>
-      <c r="F7" s="31" t="n">
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="29" t="n"/>
-      <c r="H7" s="29" t="n"/>
-      <c r="I7" s="32">
+      <c r="G7" s="28" t="n"/>
+      <c r="H7" s="28" t="n"/>
+      <c r="I7" s="31">
         <f>SUM(B7:H7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Коробка з нагрівачем</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="30" t="n">
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="31" t="n">
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="31" t="n">
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="31">
         <f>SUM(B8:H8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Разом</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="32">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="32">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>Медіана грн/100 г у смузі</t>
-        </is>
-      </c>
-      <c r="B11" s="35" t="n">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>Медіана ціни за упаковку у смузі</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="n">
         <v>171</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="34" t="n">
         <v>264</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="34" t="n">
         <v>348</v>
       </c>
-      <c r="E11" s="36" t="n">
+      <c r="E11" s="35" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="37" t="n">
+      <c r="F11" s="36" t="n">
         <v>94</v>
       </c>
-      <c r="G11" s="37" t="n">
+      <c r="G11" s="36" t="n">
         <v>104</v>
       </c>
-      <c r="H11" s="36" t="n">
+      <c r="H11" s="35" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Що показує крос-таб</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>1. Порційне вікно 200–299 г — 22 позиції (пауч 14, чаша 8). Це полиця «обід на одну людину».</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>2. Пауч живе тільки в 220–250 г: 14 із 19 позицій. Поза вікном — лише український реторт 350 г.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>3. Найщільніша клітинка — дойпак 100–149 г (16 позицій), але це сухий сублімат: інший привід.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>4. Найдешевший грам — смуга 200–249 г: 50 грн за 100 г, мінімум по всіх вагах.</t>
         </is>
@@ -4946,17 +4892,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -4996,493 +4941,433 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Грн/уп.</t>
+          <t>Ціна за упаковку</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Грн/100 г</t>
+          <t>Тип зберігання</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Тип зберігання</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
           <t>Походження</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Сільпо</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Ben's Original / Uncle Ben's Express</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>пауч 220–250 г</t>
         </is>
       </c>
-      <c r="D5" s="39" t="n">
+      <c r="D5" s="38" t="n">
         <v>11</v>
       </c>
-      <c r="E5" s="38" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>90–179</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
-        <is>
-          <t>36–81</t>
-        </is>
-      </c>
-      <c r="G5" s="40" t="inlineStr">
+      <c r="F5" s="39" t="inlineStr">
         <is>
           <t>Кімнатна · НАШ КОНКУРЕНТНИЙ СЕТ</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Mars · ЄС</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>МегаМаркет · Ultramarket</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>The Local Food по-тайськи з куркою</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>лоток 350 г</t>
         </is>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="38" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>207</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="G6" s="40" t="inlineStr">
+      <c r="F6" s="39" t="inlineStr">
         <is>
           <t>Кімнатна · НАШ КОНКУРЕНТНИЙ СЕТ</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Ашан</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>«Легко!» рис з овочами та курячим фрікасе</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>лоток 280 г</t>
         </is>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="38" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G7" s="41" t="inlineStr">
+      <c r="F7" s="40" t="inlineStr">
         <is>
           <t>Охолоджена кулінарія · 2–5 діб</t>
         </is>
       </c>
-      <c r="H7" s="26" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Сільпо</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>«Чіл Міл» рис паровий · рис з яйцем і овочами</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>лоток</t>
         </is>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E8" s="37" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
-      </c>
-      <c r="G8" s="41" t="inlineStr">
+      <c r="F8" s="40" t="inlineStr">
         <is>
           <t>Охолоджена кулінарія · 2–5 діб</t>
         </is>
       </c>
-      <c r="H8" s="26" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Сільпо</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Боули з рисом · теріякі · рис по-китайськи</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>кулінарія</t>
         </is>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D9" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="38" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>139–439</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
-      </c>
-      <c r="G9" s="41" t="inlineStr">
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>Охолоджена кулінарія · 2–5 діб</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>NOVUS</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>«Майстри Смаку» рис з овочами</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>кулінарія</t>
         </is>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D10" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="38" t="inlineStr">
+      <c r="E10" s="37" t="inlineStr">
         <is>
           <t>299</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
-      </c>
-      <c r="G10" s="41" t="inlineStr">
+      <c r="F10" s="40" t="inlineStr">
         <is>
           <t>Охолоджена кулінарія · 2–5 діб</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>МегаМаркет · Ultramarket</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Рис японський з овочами</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>кулінарія</t>
         </is>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D11" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="38" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>366</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
-      </c>
-      <c r="G11" s="41" t="inlineStr">
+      <c r="F11" s="40" t="inlineStr">
         <is>
           <t>Охолоджена кулінарія · 2–5 діб</t>
         </is>
       </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Ашан · NOVUS · МегаМаркет · Сільпо</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>«Жменька» Tasty Mix басматі з овочами</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>пакет 200 г</t>
         </is>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D12" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="38" t="inlineStr">
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>89–92</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="G12" s="42" t="inlineStr">
+      <c r="F12" s="41" t="inlineStr">
         <is>
           <t>Суміш під варіння · не готовий</t>
         </is>
       </c>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>NOVUS · Сільпо</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Trapeza басматі з карі по-індійськи</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>пакет 250 г</t>
         </is>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D13" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="38" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>59–85</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
-        <is>
-          <t>24–34</t>
-        </is>
-      </c>
-      <c r="G13" s="42" t="inlineStr">
+      <c r="F13" s="41" t="inlineStr">
         <is>
           <t>Суміш під варіння · не готовий</t>
         </is>
       </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>МегаМаркет · Ultramarket</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>«Зерновита» рис з овочами</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>пакет 500 г</t>
         </is>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="38" t="inlineStr">
+      <c r="E14" s="37" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G14" s="42" t="inlineStr">
+      <c r="F14" s="41" t="inlineStr">
         <is>
           <t>Суміш під варіння · не готовий</t>
         </is>
       </c>
-      <c r="H14" s="26" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>METRO</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>готового рису немає</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D15" s="39" t="n"/>
-      <c r="E15" s="38" t="inlineStr">
+      <c r="D15" s="38" t="n"/>
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="43" t="inlineStr">
+      <c r="F15" s="42" t="inlineStr">
         <is>
           <t>Категорії немає</t>
         </is>
       </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>лише крупа 1–10 кг</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Підсумок</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Ambient (наш конкурентний сет): 12 SKU на всю країну. 11 з них — Ben's Original у «Сільпо».</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Єдина інша ambient-позиція: The Local Food по-тайськи 350 г, 207 грн, МегаМаркет і Ultramarket.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>METRO: готового рису немає взагалі — лише крупа 1–10 кг під Metro Chef і Aro для HoReCa.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Фоззі Cash&amp;Carry перевірити не вдалося: каталог закритий ботозахистом. За аналогією з METRO (той самий формат C&amp;C) ambient-рису там також не очікується — це припущення, не факт.</t>
         </is>
@@ -5575,219 +5460,219 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Ottogi</t>
         </is>
       </c>
-      <c r="B5" s="44" t="n">
+      <c r="B5" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="45" t="n">
+      <c r="C5" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="29" t="n"/>
-      <c r="E5" s="29" t="n"/>
-      <c r="F5" s="45" t="n">
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="31">
         <f>SUM(B5:F5)</f>
         <v/>
       </c>
-      <c r="H5" s="46" t="n">
+      <c r="H5" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>локшина, рамен</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Bibigo</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
+      <c r="B6" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="29" t="n"/>
-      <c r="D6" s="29" t="n"/>
-      <c r="E6" s="29" t="n"/>
-      <c r="F6" s="29" t="n"/>
-      <c r="G6" s="32">
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="31">
         <f>SUM(B6:F6)</f>
         <v/>
       </c>
-      <c r="H6" s="46" t="n">
+      <c r="H6" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>токпокі, стір-фрай рамен</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Samyang</t>
         </is>
       </c>
-      <c r="B7" s="44" t="n">
+      <c r="B7" s="43" t="n">
         <v>17</v>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="44" t="n">
         <v>7</v>
       </c>
-      <c r="D7" s="29" t="n"/>
-      <c r="E7" s="45" t="n">
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F7" s="44" t="n">
         <v>9</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="31">
         <f>SUM(B7:F7)</f>
         <v/>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>рамен</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Nongshim</t>
         </is>
       </c>
-      <c r="B8" s="44" t="n">
+      <c r="B8" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="43" t="n">
         <v>14</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="31">
         <f>SUM(B8:F8)</f>
         <v/>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>локшина</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Paldo</t>
         </is>
       </c>
-      <c r="B9" s="44" t="n">
+      <c r="B9" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="45" t="n">
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="32">
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="31">
         <f>SUM(B9:F9)</f>
         <v/>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>локшина</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Aroy-D</t>
         </is>
       </c>
-      <c r="B10" s="44" t="n">
+      <c r="B10" s="43" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="44" t="n">
+      <c r="C10" s="43" t="n">
         <v>14</v>
       </c>
-      <c r="D10" s="45" t="n">
+      <c r="D10" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="F10" s="45" t="n">
+      <c r="F10" s="44" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="31">
         <f>SUM(B10:F10)</f>
         <v/>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>соуси, пасти, кокос</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Що це означає</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>1. Ottogi має 14 позицій у трьох мережах, Bibigo — 6 в «Ашані». Імпортер, лістинг і полиця вже існують.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>2. Ті самі Ottogi і Bibigo продають чаші з рисом по 225–356 грн — але лише в азійських фудшопах.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>3. Бар'єр входу азійського рису в мережу — не дистрибуція, а те, що ніхто цього не зробив.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>4. Ризик: імпортер Ottogi додасть рисові SKU до наявного лістингу швидше, ніж ми збудуємо свій.</t>
         </is>
@@ -5830,112 +5715,112 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Курс, грн/$</t>
         </is>
       </c>
-      <c r="B4" s="48" t="n">
+      <c r="B4" s="47" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Бонус мережі, %</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="48" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Цільова маржа, %</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="48" t="n">
         <v>0.35</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>Націнка мережі (x)</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n">
+      <c r="B7" s="47" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>Частка ціни для собівартості</t>
         </is>
       </c>
-      <c r="B8" s="50">
+      <c r="B8" s="49">
         <f>1-B5-B6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Коеф. FOB → СС, 20′ FCL</t>
         </is>
       </c>
-      <c r="B9" s="51" t="n">
+      <c r="B9" s="50" t="n">
         <v>1.70740755878359</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Коеф. FOB → СС, 40′ FCL</t>
         </is>
       </c>
-      <c r="B10" s="51" t="n">
+      <c r="B10" s="50" t="n">
         <v>1.530558573152913</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="52" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>Полиця = СС_грн × націнка / частка_СС</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>Множник СС → полиця</t>
         </is>
       </c>
-      <c r="B12" s="53">
+      <c r="B12" s="52">
         <f>B7/B8</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>Множник FOB → полиця, 20′ FCL</t>
         </is>
       </c>
-      <c r="B13" s="54">
+      <c r="B13" s="53">
         <f>B9*B4*B12</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>Множник FOB → полиця, 40′ FCL</t>
         </is>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="53">
         <f>B10*B4*B12</f>
         <v/>
       </c>
@@ -5973,222 +5858,222 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="55" t="n">
+      <c r="A18" s="54" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Ben's Original медіана 41 грн/100 г при 240 г</t>
         </is>
       </c>
-      <c r="C18" s="56">
+      <c r="C18" s="55">
         <f>A18/$B$12</f>
         <v/>
       </c>
-      <c r="D18" s="57">
+      <c r="D18" s="56">
         <f>C18/$B$4</f>
         <v/>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="57">
         <f>A18/$B$13</f>
         <v/>
       </c>
-      <c r="F18" s="58">
+      <c r="F18" s="57">
         <f>A18/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="59" t="n">
+      <c r="A19" s="58" t="n">
         <v>109</v>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>Медіана формату «пауч» — найдешевший вхід у мережу</t>
         </is>
       </c>
-      <c r="C19" s="61">
+      <c r="C19" s="60">
         <f>A19/$B$12</f>
         <v/>
       </c>
-      <c r="D19" s="62">
+      <c r="D19" s="61">
         <f>C19/$B$4</f>
         <v/>
       </c>
-      <c r="E19" s="63">
+      <c r="E19" s="62">
         <f>A19/$B$13</f>
         <v/>
       </c>
-      <c r="F19" s="63">
+      <c r="F19" s="62">
         <f>A19/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="55" t="n">
+      <c r="A20" s="54" t="n">
         <v>119</v>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Агресивний сценарій для стакана 150 г</t>
         </is>
       </c>
-      <c r="C20" s="56">
+      <c r="C20" s="55">
         <f>A20/$B$12</f>
         <v/>
       </c>
-      <c r="D20" s="57">
+      <c r="D20" s="56">
         <f>C20/$B$4</f>
         <v/>
       </c>
-      <c r="E20" s="58">
+      <c r="E20" s="57">
         <f>A20/$B$13</f>
         <v/>
       </c>
-      <c r="F20" s="58">
+      <c r="F20" s="57">
         <f>A20/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="59" t="n">
+      <c r="A21" s="58" t="n">
         <v>129</v>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>РЕКОМЕНДОВАНО для стакана 150 г — нижче Henan-медіани</t>
         </is>
       </c>
-      <c r="C21" s="61">
+      <c r="C21" s="60">
         <f>A21/$B$12</f>
         <v/>
       </c>
-      <c r="D21" s="62">
+      <c r="D21" s="61">
         <f>C21/$B$4</f>
         <v/>
       </c>
-      <c r="E21" s="63">
+      <c r="E21" s="62">
         <f>A21/$B$13</f>
         <v/>
       </c>
-      <c r="F21" s="63">
+      <c r="F21" s="62">
         <f>A21/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="55" t="n">
+      <c r="A22" s="54" t="n">
         <v>139</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Поточна полиця стакана 150 г без переговорів</t>
         </is>
       </c>
-      <c r="C22" s="56">
+      <c r="C22" s="55">
         <f>A22/$B$12</f>
         <v/>
       </c>
-      <c r="D22" s="57">
+      <c r="D22" s="56">
         <f>C22/$B$4</f>
         <v/>
       </c>
-      <c r="E22" s="58">
+      <c r="E22" s="57">
         <f>A22/$B$13</f>
         <v/>
       </c>
-      <c r="F22" s="58">
+      <c r="F22" s="57">
         <f>A22/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="59" t="n">
+      <c r="A23" s="58" t="n">
         <v>155</v>
       </c>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="59" t="inlineStr">
         <is>
           <t>Паритет із Bibigo 210 г (135–189 грн)</t>
         </is>
       </c>
-      <c r="C23" s="61">
+      <c r="C23" s="60">
         <f>A23/$B$12</f>
         <v/>
       </c>
-      <c r="D23" s="62">
+      <c r="D23" s="61">
         <f>C23/$B$4</f>
         <v/>
       </c>
-      <c r="E23" s="63">
+      <c r="E23" s="62">
         <f>A23/$B$13</f>
         <v/>
       </c>
-      <c r="F23" s="63">
+      <c r="F23" s="62">
         <f>A23/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55" t="n">
+      <c r="A24" s="54" t="n">
         <v>179</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Верх вікна мережевої полиці</t>
         </is>
       </c>
-      <c r="C24" s="56">
+      <c r="C24" s="55">
         <f>A24/$B$12</f>
         <v/>
       </c>
-      <c r="D24" s="57">
+      <c r="D24" s="56">
         <f>C24/$B$4</f>
         <v/>
       </c>
-      <c r="E24" s="58">
+      <c r="E24" s="57">
         <f>A24/$B$13</f>
         <v/>
       </c>
-      <c r="F24" s="58">
+      <c r="F24" s="57">
         <f>A24/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="59" t="n">
+      <c r="A25" s="58" t="n">
         <v>199</v>
       </c>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="B25" s="59" t="inlineStr">
         <is>
           <t>Ottogi −22 % — стеля для лотка ONE'S 200 г</t>
         </is>
       </c>
-      <c r="C25" s="61">
+      <c r="C25" s="60">
         <f>A25/$B$12</f>
         <v/>
       </c>
-      <c r="D25" s="62">
+      <c r="D25" s="61">
         <f>C25/$B$4</f>
         <v/>
       </c>
-      <c r="E25" s="63">
+      <c r="E25" s="62">
         <f>A25/$B$13</f>
         <v/>
       </c>
-      <c r="F25" s="63">
+      <c r="F25" s="62">
         <f>A25/$B$14</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Правило для переговорів</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Кожні $0,10 зниження FOB знімають ~27 грн з полиці (20′ FCL). Перехід із 20′ на 40′ FCL дає ~−11 % собівартості без переговорів із постачальником.</t>
         </is>
@@ -6251,264 +6136,264 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Ціни конкурентів на полиці</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>ФАКТ</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Картки продавців, 17 мереж zakaz.ua, «Сільпо», Prom, Rozetka, MAUDAU, 22–23.09.2026</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="64" t="inlineStr">
+      <c r="A6" s="63" t="inlineStr">
         <is>
           <t>Формати, ваги, кількість SKU</t>
         </is>
       </c>
-      <c r="B6" s="65" t="inlineStr">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>ФАКТ</t>
         </is>
       </c>
-      <c r="C6" s="66" t="inlineStr">
+      <c r="C6" s="65" t="inlineStr">
         <is>
           <t>Картки продавців. 2 позиції без маси виключено з грн/100 г</t>
         </is>
       </c>
-      <c r="D6" s="67" t="inlineStr">
+      <c r="D6" s="66" t="inlineStr">
         <is>
           <t>Незначний</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Обсяг імпорту 182 т</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>ФАКТ</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Eurostat Comext CN 1904 90 10 + UN Comtrade</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="64" t="inlineStr">
+      <c r="A8" s="63" t="inlineStr">
         <is>
           <t>Ємність роздрібу 87–110 млн грн</t>
         </is>
       </c>
-      <c r="B8" s="68" t="inlineStr">
+      <c r="B8" s="67" t="inlineStr">
         <is>
           <t>ОЦІНКА</t>
         </is>
       </c>
-      <c r="C8" s="66" t="inlineStr">
+      <c r="C8" s="65" t="inlineStr">
         <is>
           <t>Імпорт × 2,2–2,8. Заміряних продажів немає</t>
         </is>
       </c>
-      <c r="D8" s="67" t="inlineStr">
+      <c r="D8" s="66" t="inlineStr">
         <is>
           <t>Похибка ±30 % у бізнес-кейсі</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>Собівартість BSCM і CM Premium</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>ФАКТ</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Комерційні пропозиції, RTE_Rice_Suppliers.pptx</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="64" t="inlineStr">
+      <c r="A10" s="63" t="inlineStr">
         <is>
           <t>FOB ONE'S International</t>
         </is>
       </c>
-      <c r="B10" s="68" t="inlineStr">
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>ОЦІНКА</t>
         </is>
       </c>
-      <c r="C10" s="66" t="inlineStr">
+      <c r="C10" s="65" t="inlineStr">
         <is>
           <t>Виведено з СС за коефіцієнтом 1,7074. Постачальник FOB не розкрив</t>
         </is>
       </c>
-      <c r="D10" s="67" t="inlineStr">
+      <c r="D10" s="66" t="inlineStr">
         <is>
           <t>Рекомендація по Fried Rice 200 г може бути хибною</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>Коеф. FOB → СС = 1,7074</t>
         </is>
       </c>
-      <c r="B11" s="41" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>РОЗРАХУНОК</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>СС / FOB для BSCM Jasmine 240 г, перевірено на 15 SKU</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Зсув усіх цільових FOB</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="64" t="inlineStr">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>Мито 10 % у собівартості</t>
         </is>
       </c>
-      <c r="B12" s="69" t="inlineStr">
+      <c r="B12" s="68" t="inlineStr">
         <is>
           <t>ПРИПУЩЕННЯ</t>
         </is>
       </c>
-      <c r="C12" s="66" t="inlineStr">
+      <c r="C12" s="65" t="inlineStr">
         <is>
           <t>Зазначено в RTE_Rice_Suppliers. Первинне джерело не наведено</t>
         </is>
       </c>
-      <c r="D12" s="67" t="inlineStr">
+      <c r="D12" s="66" t="inlineStr">
         <is>
           <t>±27 грн на полиці</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Імпортний ПДВ 20 % у СС</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>РИЗИК</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Ймовірне задвоєння: ПДВ і у витратах, і в ціні «вже з ПДВ»</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>СС −16,7 %, полиця пауча 157 → 131 грн</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="64" t="inlineStr">
+      <c r="A14" s="63" t="inlineStr">
         <is>
           <t>Бонус мережі 25 %</t>
         </is>
       </c>
-      <c r="B14" s="69" t="inlineStr">
+      <c r="B14" s="68" t="inlineStr">
         <is>
           <t>ПРИПУЩЕННЯ</t>
         </is>
       </c>
-      <c r="C14" s="66" t="inlineStr">
+      <c r="C14" s="65" t="inlineStr">
         <is>
           <t>Взято з прикладу по локшині. Умови «Сільпо» не запитані</t>
         </is>
       </c>
-      <c r="D14" s="67" t="inlineStr">
+      <c r="D14" s="66" t="inlineStr">
         <is>
           <t>За 30 % полиця +17 %</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>«Маржа 35 %»</t>
         </is>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>ВИЗНАЧЕННЯ</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Валова націнка. Не містить ФОП, маркетингу, лістингу, списань</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>Не є чистою рентабельністю</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="64" t="inlineStr">
+      <c r="A16" s="63" t="inlineStr">
         <is>
           <t>Оборотність Ben's у «Сільпо»</t>
         </is>
       </c>
-      <c r="B16" s="70" t="inlineStr">
+      <c r="B16" s="69" t="inlineStr">
         <is>
           <t>НЕМАЄ ДАНИХ</t>
         </is>
       </c>
-      <c r="C16" s="66" t="inlineStr">
+      <c r="C16" s="65" t="inlineStr">
         <is>
           <t>Мережа обсягів не віддає</t>
         </is>
       </c>
-      <c r="D16" s="67" t="inlineStr">
+      <c r="D16" s="66" t="inlineStr">
         <is>
           <t>Неможливо порахувати план продажів</t>
         </is>

--- a/rte-rice-analysis/RTE_Rice_Benchmark.xlsx
+++ b/rte-rice-analysis/RTE_Rice_Benchmark.xlsx
@@ -2009,7 +2009,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Розподіл 84 позицій. грн/100 г = медіана ціни формату / медіану ваги формату.</t>
+          <t>Розподіл 84 позицій за типом паковання. Ціна — роздріб за одну упаковку.</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>4. Найдешевший грам — смуга 200–249 г: 50 грн за 100 г, мінімум по всіх вагах.</t>
+          <t>4. Чаша — єдиний формат, присутній у шести вагових смугах із семи.</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Ben's Original медіана 41 грн/100 г при 240 г</t>
+          <t>Рівень медіани Ben's Original — 90 грн за упаковку</t>
         </is>
       </c>
       <c r="C18" s="55">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="C6" s="65" t="inlineStr">
         <is>
-          <t>Картки продавців. 2 позиції без маси виключено з грн/100 г</t>
+          <t>Картки продавців. 2 позиції без указаної маси (Trek'n Eat)</t>
         </is>
       </c>
       <c r="D6" s="66" t="inlineStr">
